--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="36">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -895,7 +898,7 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -923,14 +926,17 @@
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
@@ -951,14 +957,14 @@
       <c r="I2" s="1">
         <v>0.05</v>
       </c>
-      <c r="J2" s="1">
-        <v>0</v>
-      </c>
       <c r="K2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
@@ -979,14 +985,14 @@
       <c r="I3" s="1">
         <v>0.05</v>
       </c>
-      <c r="J3" s="1">
-        <v>0</v>
-      </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
@@ -1007,14 +1013,14 @@
       <c r="I4" s="1">
         <v>0.05</v>
       </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
       <c r="K4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
@@ -1033,14 +1039,14 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
       <c r="K5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
@@ -1059,14 +1065,14 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
@@ -1085,14 +1091,14 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
@@ -1113,14 +1119,14 @@
       <c r="I8" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
@@ -1141,14 +1147,14 @@
       <c r="I9" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
@@ -1169,14 +1175,14 @@
       <c r="I10" s="1">
         <v>0.20000000000000001</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>90004</v>
       </c>
@@ -1195,14 +1201,14 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
       <c r="K11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
@@ -1221,14 +1227,14 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
       <c r="K12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
@@ -1247,14 +1253,14 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1">
-        <v>0</v>
-      </c>
       <c r="K13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <v>90005</v>
       </c>
@@ -1271,18 +1277,19 @@
         <v>3</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="0">
         <v>2</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
       <c r="K14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
@@ -1299,18 +1306,19 @@
         <v>5</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="0">
         <v>2</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
       <c r="K15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
@@ -1327,18 +1335,19 @@
         <v>7</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="0">
         <v>3</v>
       </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
       <c r="K16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1">
         <v>90006</v>
       </c>
@@ -1359,14 +1368,14 @@
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
@@ -1387,14 +1396,14 @@
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
       <c r="K18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1">
         <v>90006</v>
       </c>
@@ -1415,14 +1424,14 @@
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
       <c r="K19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1">
         <v>90007</v>
       </c>
@@ -1443,14 +1452,14 @@
       <c r="I20" s="1">
         <v>0.05</v>
       </c>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
       <c r="K20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1">
         <v>90007</v>
       </c>
@@ -1471,14 +1480,14 @@
       <c r="I21" s="1">
         <v>0.05</v>
       </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
       <c r="K21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1">
         <v>90007</v>
       </c>
@@ -1499,14 +1508,14 @@
       <c r="I22" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
       <c r="K22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="6:9">
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -11,122 +11,121 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId5"/>
     <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="37">
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+    <t xml:space="preserve">icon_id</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
   </si>
 </sst>
 </file>
@@ -641,19 +640,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -678,42 +677,43 @@
     <col min="4" max="4" width="15.640625" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.640625" customWidth="1"/>
+    <col min="7" max="7" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -721,19 +721,19 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -747,19 +747,19 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F3" s="1">
         <v>15</v>
       </c>
       <c r="G3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -773,19 +773,19 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F4" s="1">
         <v>25</v>
       </c>
       <c r="G4" s="1">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
@@ -799,19 +799,19 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -825,19 +825,19 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -851,19 +851,19 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -900,40 +900,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -941,13 +941,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -969,13 +969,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1">
         <v>10</v>
@@ -997,13 +997,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1">
         <v>25</v>
@@ -1025,13 +1025,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1051,13 +1051,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -1077,13 +1077,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -1103,13 +1103,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1">
         <v>15</v>
@@ -1131,13 +1131,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -1159,13 +1159,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="1">
         <v>40</v>
@@ -1187,13 +1187,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
@@ -1213,13 +1213,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1239,13 +1239,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1">
         <v>100</v>
@@ -1265,13 +1265,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
@@ -1294,13 +1294,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
@@ -1323,13 +1323,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F16" s="1">
         <v>7</v>
@@ -1352,13 +1352,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1">
         <v>20</v>
@@ -1380,19 +1380,19 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1">
         <v>30</v>
       </c>
       <c r="G18" s="1">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1408,19 +1408,19 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F19" s="1">
         <v>50</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1436,10 +1436,10 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>24</v>
@@ -1464,10 +1464,10 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>24</v>
@@ -1492,10 +1492,10 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>24</v>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="6:10">
+    <row r="23" spans="6:9">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="37">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,119 +16,122 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="37">
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-</sst>
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>id</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>attack_interval</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>critical_damage</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>attack_range</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>attack_count</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>attack_damage</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>critical_chance</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>upgrade_name</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>절대무적_요새_288버켓</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>절대무적_요새_멜리에스클래식_몸통뉴</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_KMD_08_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_MEL_05_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_KMD_10_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_288_19_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>폭발 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>description</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>냉기 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_KMD_12_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_MEL_16_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Weapon_MEL_14_UI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>max_hp</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>icon_id</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>기관총 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>화염 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>미사일 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>레이저 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>포격 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>전기 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>저격 포탑 강화</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>target_count</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>attack_area</ns0:t>
+  </ns0:si>
+</ns0:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +671,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
@@ -703,16 +706,19 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -735,10 +741,13 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="J2" s="1">
+      <c r="H2">
         <v>0</v>
       </c>
       <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -761,10 +770,13 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="J3" s="1">
+      <c r="H3">
         <v>0</v>
       </c>
       <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -787,10 +799,13 @@
       <c r="G4" s="1">
         <v>4</v>
       </c>
-      <c r="J4" s="1">
+      <c r="H4">
         <v>0</v>
       </c>
       <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -813,10 +828,13 @@
       <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="J5" s="1">
+      <c r="H5">
         <v>0</v>
       </c>
       <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -839,10 +857,13 @@
       <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="J6" s="1">
+      <c r="H6">
         <v>0</v>
       </c>
       <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -865,16 +886,22 @@
       <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="J7" s="1">
+      <c r="H7">
         <v>0</v>
       </c>
       <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="6:7">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
+      <c r="H8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -883,7 +910,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
@@ -920,19 +947,22 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -953,14 +983,17 @@
         <v>5</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1">
         <v>0.05</v>
       </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
       <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -981,14 +1014,17 @@
         <v>10</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1">
         <v>0.05</v>
       </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
       <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1009,14 +1045,17 @@
         <v>25</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1">
         <v>0.05</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
       <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1037,12 +1076,15 @@
         <v>2</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="H5">
+        <v>0</v>
+      </c>
       <c r="I5" s="1"/>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
+      <c r="J5" s="1"/>
       <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1063,12 +1105,15 @@
         <v>3</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="H6">
+        <v>0</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
+      <c r="J6" s="1"/>
       <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1089,12 +1134,15 @@
         <v>6</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
+      <c r="H7">
+        <v>0</v>
+      </c>
       <c r="I7" s="1"/>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
+      <c r="J7" s="1"/>
       <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1115,14 +1163,17 @@
         <v>15</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
       <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1143,14 +1194,17 @@
         <v>20</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
       <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1171,14 +1225,17 @@
         <v>40</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
         <v>0.20000000000000001</v>
       </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
       <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1199,12 +1256,15 @@
         <v>50</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
+      <c r="H11">
+        <v>0</v>
+      </c>
       <c r="I11" s="1"/>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
+      <c r="J11" s="1"/>
       <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1225,12 +1285,15 @@
         <v>50</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="H12">
+        <v>0</v>
+      </c>
       <c r="I12" s="1"/>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
+      <c r="J12" s="1"/>
       <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1251,12 +1314,15 @@
         <v>100</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="I13" s="1"/>
-      <c r="K13" s="1">
-        <v>0</v>
-      </c>
+      <c r="J13" s="1"/>
       <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1277,15 +1343,18 @@
         <v>3</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
+      <c r="H14">
+        <v>0</v>
+      </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="0">
+      <c r="J14" s="1"/>
+      <c r="K14" s="0">
         <v>2</v>
       </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
       <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1306,15 +1375,18 @@
         <v>5</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="H15">
+        <v>0</v>
+      </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="0">
+      <c r="J15" s="1"/>
+      <c r="K15" s="0">
         <v>2</v>
       </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
       <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1335,15 +1407,18 @@
         <v>7</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="H16">
+        <v>0</v>
+      </c>
       <c r="I16" s="1"/>
-      <c r="J16" s="0">
+      <c r="J16" s="1"/>
+      <c r="K16" s="0">
         <v>3</v>
       </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
       <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1366,12 +1441,15 @@
       <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17">
+        <v>0</v>
+      </c>
       <c r="I17" s="1"/>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
+      <c r="J17" s="1"/>
       <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1394,12 +1472,15 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18">
+        <v>0</v>
+      </c>
       <c r="I18" s="1"/>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
+      <c r="J18" s="1"/>
       <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1422,12 +1503,15 @@
       <c r="G19" s="1">
         <v>4</v>
       </c>
-      <c r="H19" s="1"/>
+      <c r="H19">
+        <v>0</v>
+      </c>
       <c r="I19" s="1"/>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
+      <c r="J19" s="1"/>
       <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1448,14 +1532,17 @@
         <v>50</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1">
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1">
         <v>0.05</v>
       </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
       <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1476,14 +1563,17 @@
         <v>75</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1">
         <v>0.05</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
       <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1504,22 +1594,28 @@
         <v>125</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
         <v>0.14999999999999999</v>
       </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
       <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="H23">
+        <v>0</v>
+      </c>
       <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,122 +16,137 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>id</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_interval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>critical_damage</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_range</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_count</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_damage</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>critical_chance</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>upgrade_name</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>절대무적_요새_288버켓</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>절대무적_요새_멜리에스클래식_몸통뉴</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_08_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_05_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_10_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_288_19_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>폭발 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>description</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>냉기 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_12_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_16_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_14_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>max_hp</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>icon_id</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>기관총 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>화염 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>미사일 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>레이저 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>포격 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>전기 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>저격 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>target_count</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_area</ns0:t>
-  </ns0:si>
-</ns0:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="43">
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 속사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 후 0.2초 간격으로 3회 추가 발사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 광역 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -671,9 +686,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
@@ -706,7 +721,7 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -741,7 +756,7 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="K2" s="1">
@@ -770,7 +785,7 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -799,7 +814,7 @@
       <c r="G4" s="1">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>0</v>
       </c>
       <c r="K4" s="1">
@@ -828,7 +843,7 @@
       <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="K5" s="1">
@@ -857,7 +872,7 @@
       <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="K6" s="1">
@@ -886,7 +901,7 @@
       <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>0</v>
       </c>
       <c r="K7" s="1">
@@ -899,7 +914,7 @@
     <row r="8" spans="6:7">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>0</v>
       </c>
     </row>
@@ -910,9 +925,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -925,7 +940,7 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -947,7 +962,7 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -964,6 +979,9 @@
       </c>
       <c r="M1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -983,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="I2" s="1"/>
@@ -1014,7 +1032,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
@@ -1045,7 +1063,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>0</v>
       </c>
       <c r="I4" s="1"/>
@@ -1076,7 +1094,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="I5" s="1"/>
@@ -1105,7 +1123,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="I6" s="1"/>
@@ -1134,7 +1152,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>0</v>
       </c>
       <c r="I7" s="1"/>
@@ -1163,7 +1181,7 @@
         <v>15</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>0</v>
       </c>
       <c r="I8" s="1"/>
@@ -1194,7 +1212,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9">
+      <c r="H9" s="0">
         <v>0</v>
       </c>
       <c r="I9" s="1"/>
@@ -1225,7 +1243,7 @@
         <v>40</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10">
+      <c r="H10" s="0">
         <v>0</v>
       </c>
       <c r="I10" s="1"/>
@@ -1256,7 +1274,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11">
+      <c r="H11" s="0">
         <v>0</v>
       </c>
       <c r="I11" s="1"/>
@@ -1285,7 +1303,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12">
+      <c r="H12" s="0">
         <v>0</v>
       </c>
       <c r="I12" s="1"/>
@@ -1314,7 +1332,7 @@
         <v>100</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13">
+      <c r="H13" s="0">
         <v>0</v>
       </c>
       <c r="I13" s="1"/>
@@ -1343,7 +1361,7 @@
         <v>3</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14">
+      <c r="H14" s="0">
         <v>0</v>
       </c>
       <c r="I14" s="1"/>
@@ -1375,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15">
+      <c r="H15" s="0">
         <v>0</v>
       </c>
       <c r="I15" s="1"/>
@@ -1407,7 +1425,7 @@
         <v>7</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16">
+      <c r="H16" s="0">
         <v>0</v>
       </c>
       <c r="I16" s="1"/>
@@ -1441,7 +1459,7 @@
       <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="0">
         <v>0</v>
       </c>
       <c r="I17" s="1"/>
@@ -1472,7 +1490,7 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="0">
         <v>0</v>
       </c>
       <c r="I18" s="1"/>
@@ -1503,7 +1521,7 @@
       <c r="G19" s="1">
         <v>4</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="0">
         <v>0</v>
       </c>
       <c r="I19" s="1"/>
@@ -1532,7 +1550,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20">
+      <c r="H20" s="0">
         <v>0</v>
       </c>
       <c r="I20" s="1"/>
@@ -1563,7 +1581,7 @@
         <v>75</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="H21">
+      <c r="H21" s="0">
         <v>0</v>
       </c>
       <c r="I21" s="1"/>
@@ -1594,7 +1612,7 @@
         <v>125</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22">
+      <c r="H22" s="0">
         <v>0</v>
       </c>
       <c r="I22" s="1"/>
@@ -1611,11 +1629,166 @@
     <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23">
+      <c r="H23" s="0">
         <v>0</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="1">
+        <v>90008</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="1">
+        <v>90009</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="1">
+        <v>150</v>
+      </c>
+      <c r="G25" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="1">
+        <v>90009</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1">
+        <v>200</v>
+      </c>
+      <c r="G26" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="1">
+        <v>90009</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1">
+        <v>300</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -11,127 +11,126 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId5"/>
     <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>id</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_interval</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>critical_damage</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_range</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_count</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_damage</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>critical_chance</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>upgrade_name</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>절대무적_요새_288버켓</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>절대무적_요새_멜리에스클래식_몸통뉴</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_08_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_05_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_10_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_288_19_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>폭발 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>description</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>냉기 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_KMD_12_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_16_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>Weapon_MEL_14_UI</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>max_hp</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>icon_id</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>기관총 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>화염 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>미사일 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>레이저 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>포격 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>전기 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>저격 포탑 강화</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>target_count</ns0:t>
-  </ns0:si>
-  <ns0:si>
-    <ns0:t>attack_area</ns0:t>
-  </ns0:si>
-</ns0:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="38">
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -644,19 +643,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -671,9 +670,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
@@ -684,56 +683,56 @@
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
@@ -741,7 +740,7 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="K2" s="1">
@@ -751,18 +750,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1">
         <v>15</v>
@@ -770,7 +769,7 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -780,18 +779,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1">
         <v>25</v>
@@ -799,7 +798,7 @@
       <c r="G4" s="1">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>0</v>
       </c>
       <c r="K4" s="1">
@@ -809,18 +808,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -828,7 +827,7 @@
       <c r="G5" s="1">
         <v>2</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="K5" s="1">
@@ -838,18 +837,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -857,7 +856,7 @@
       <c r="G6" s="1">
         <v>3</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="K6" s="1">
@@ -867,18 +866,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -886,7 +885,7 @@
       <c r="G7" s="1">
         <v>4</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>0</v>
       </c>
       <c r="K7" s="1">
@@ -899,9 +898,6 @@
     <row r="8" spans="6:7">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -910,9 +906,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -923,67 +919,68 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="I2" s="1"/>
@@ -997,24 +994,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1">
         <v>10</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
@@ -1028,24 +1025,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
         <v>25</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>0</v>
       </c>
       <c r="I4" s="1"/>
@@ -1059,24 +1056,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="I5" s="1"/>
@@ -1088,24 +1085,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>0</v>
       </c>
       <c r="I6" s="1"/>
@@ -1117,24 +1114,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>0</v>
       </c>
       <c r="I7" s="1"/>
@@ -1146,29 +1143,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
         <v>15</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8">
+      <c r="H8" s="0">
         <v>0</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1177,29 +1174,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9">
+      <c r="H9" s="0">
         <v>0</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1208,24 +1205,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
         <v>40</v>
       </c>
       <c r="G10" s="1"/>
-      <c r="H10">
+      <c r="H10" s="0">
         <v>0</v>
       </c>
       <c r="I10" s="1"/>
@@ -1239,24 +1236,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1">
         <v>50</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11">
+      <c r="H11" s="0">
         <v>0</v>
       </c>
       <c r="I11" s="1"/>
@@ -1268,24 +1265,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12">
+      <c r="H12" s="0">
         <v>0</v>
       </c>
       <c r="I12" s="1"/>
@@ -1297,24 +1294,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1">
         <v>100</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13">
+      <c r="H13" s="0">
         <v>0</v>
       </c>
       <c r="I13" s="1"/>
@@ -1326,24 +1323,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1">
         <v>3</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14">
+      <c r="H14" s="0">
         <v>0</v>
       </c>
       <c r="I14" s="1"/>
@@ -1358,24 +1355,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15">
+      <c r="H15" s="0">
         <v>0</v>
       </c>
       <c r="I15" s="1"/>
@@ -1390,24 +1387,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1">
         <v>7</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16">
+      <c r="H16" s="0">
         <v>0</v>
       </c>
       <c r="I16" s="1"/>
@@ -1422,18 +1419,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1">
         <v>20</v>
@@ -1441,7 +1438,7 @@
       <c r="G17" s="1">
         <v>1</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="0">
         <v>0</v>
       </c>
       <c r="I17" s="1"/>
@@ -1453,18 +1450,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F18" s="1">
         <v>30</v>
@@ -1472,7 +1469,7 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="0">
         <v>0</v>
       </c>
       <c r="I18" s="1"/>
@@ -1484,18 +1481,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F19" s="1">
         <v>50</v>
@@ -1503,7 +1500,7 @@
       <c r="G19" s="1">
         <v>4</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="0">
         <v>0</v>
       </c>
       <c r="I19" s="1"/>
@@ -1515,24 +1512,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1">
         <v>50</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20">
+      <c r="H20" s="0">
         <v>0</v>
       </c>
       <c r="I20" s="1"/>
@@ -1546,24 +1543,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1">
         <v>75</v>
       </c>
       <c r="G21" s="1"/>
-      <c r="H21">
+      <c r="H21" s="0">
         <v>0</v>
       </c>
       <c r="I21" s="1"/>
@@ -1577,24 +1574,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F22" s="1">
         <v>125</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="H22">
+      <c r="H22" s="0">
         <v>0</v>
       </c>
       <c r="I22" s="1"/>
@@ -1611,9 +1608,6 @@
     <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23">
-        <v>0</v>
-      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
     </row>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="38">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,114 +15,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="40">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_MEL_05_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_MEL_16_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">레이저 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
+    <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
@@ -643,19 +649,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -680,45 +686,46 @@
     <col min="4" max="4" width="15.640625" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.640625" customWidth="1"/>
+    <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -726,22 +733,20 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="0">
         <v>1</v>
-      </c>
-      <c r="H2" s="0">
-        <v>0</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -755,22 +760,20 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="0">
         <v>2</v>
-      </c>
-      <c r="H3" s="0">
-        <v>0</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -784,22 +787,20 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
-      </c>
-      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="0">
         <v>4</v>
-      </c>
-      <c r="H4" s="0">
-        <v>0</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -813,22 +814,20 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="0">
         <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="0">
-        <v>0</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -842,22 +841,20 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="0">
         <v>2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="0">
-        <v>0</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -871,22 +868,20 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="0">
         <v>4</v>
-      </c>
-      <c r="H7" s="0">
-        <v>0</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -919,48 +914,48 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="9.00390625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -968,16 +963,16 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -985,7 +980,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1">
-        <v>0.05</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -999,24 +994,24 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1">
-        <v>0.05</v>
+      <c r="J3" s="0">
+        <v>0.34999999999999998</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1030,16 +1025,16 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
@@ -1047,7 +1042,7 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1061,16 +1056,16 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="0">
@@ -1090,16 +1085,16 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="0">
@@ -1119,16 +1114,16 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
@@ -1148,16 +1143,16 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="0">
@@ -1165,7 +1160,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.05</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1179,16 +1174,16 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="0">
@@ -1196,7 +1191,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1210,16 +1205,16 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="0">
@@ -1227,7 +1222,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
-        <v>0.20000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1241,16 +1236,16 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="0">
@@ -1270,13 +1265,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1299,16 +1294,16 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="0">
@@ -1328,16 +1323,16 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="0">
@@ -1346,7 +1341,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1360,16 +1355,16 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="1">
         <v>4</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="0">
@@ -1378,7 +1373,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -1392,16 +1387,16 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="0">
@@ -1424,22 +1419,20 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1">
-        <v>20</v>
-      </c>
-      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="0">
         <v>1</v>
-      </c>
-      <c r="H17" s="0">
-        <v>0</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1455,22 +1448,20 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1">
-        <v>30</v>
-      </c>
-      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="0">
         <v>2</v>
-      </c>
-      <c r="H18" s="0">
-        <v>0</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1486,22 +1477,20 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="1">
+        <v>20</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="0">
         <v>3</v>
-      </c>
-      <c r="F19" s="1">
-        <v>50</v>
-      </c>
-      <c r="G19" s="1">
-        <v>4</v>
-      </c>
-      <c r="H19" s="0">
-        <v>0</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1517,16 +1506,16 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F20" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="0">
@@ -1534,7 +1523,7 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -1548,16 +1537,16 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F21" s="1">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="0">
@@ -1565,7 +1554,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.05</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1579,16 +1568,16 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="0">
@@ -1596,7 +1585,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="40">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -11,140 +11,139 @@
     <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId5"/>
     <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_interval</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_damage</t>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
   </si>
   <si>
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_count</t>
+    <t xml:space="preserve">upgrade_name</t>
   </si>
   <si>
     <t xml:space="preserve">attack_damage</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">폭발 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">냉기 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+    <t xml:space="preserve">icon_id</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 속사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 후 0.2초 간격으로 3회 추가 발사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 광역 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004</t>
   </si>
 </sst>
 </file>
@@ -659,19 +658,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -696,69 +695,68 @@
     <col min="4" max="4" width="15.640625" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.640625" customWidth="1"/>
+    <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="0">
         <v>1</v>
       </c>
-      <c r="H2" s="0">
-        <v>0</v>
-      </c>
       <c r="K2" s="1">
         <v>0</v>
       </c>
@@ -766,28 +764,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1"/>
+      <c r="H3" s="0">
         <v>2</v>
       </c>
-      <c r="H3" s="0">
-        <v>0</v>
-      </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
@@ -795,28 +791,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
-      </c>
-      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="0">
         <v>4</v>
       </c>
-      <c r="H4" s="0">
-        <v>0</v>
-      </c>
       <c r="K4" s="1">
         <v>0</v>
       </c>
@@ -824,28 +818,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="0">
         <v>1</v>
       </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="0">
-        <v>0</v>
-      </c>
       <c r="K5" s="1">
         <v>0</v>
       </c>
@@ -853,28 +845,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="0">
         <v>2</v>
       </c>
-      <c r="G6" s="1">
-        <v>3</v>
-      </c>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
@@ -882,27 +872,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="0">
         <v>4</v>
-      </c>
-      <c r="H7" s="0">
-        <v>0</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -914,9 +902,6 @@
     <row r="8" spans="6:7">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -927,7 +912,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -938,67 +923,68 @@
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -1006,7 +992,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1">
-        <v>0.05</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1015,29 +1001,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1">
-        <v>0.05</v>
+      <c r="J3" s="0">
+        <v>0.34999999999999998</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1046,21 +1032,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
@@ -1068,7 +1054,7 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1077,21 +1063,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="0">
@@ -1106,21 +1092,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="0">
@@ -1135,21 +1121,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
@@ -1164,21 +1150,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="0">
@@ -1186,7 +1172,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.05</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1195,21 +1181,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="0">
@@ -1217,7 +1203,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.1</v>
+        <v>0.23999999999999999</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1226,21 +1212,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="0">
@@ -1248,7 +1234,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
-        <v>0.20000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1257,21 +1243,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F11" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="0">
@@ -1286,18 +1272,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1315,21 +1301,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="0">
@@ -1344,21 +1330,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="0">
@@ -1367,7 +1353,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -1376,21 +1362,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="0">
@@ -1399,7 +1385,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -1408,21 +1394,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F16" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="0">
@@ -1440,27 +1426,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1">
-        <v>20</v>
-      </c>
-      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="0">
         <v>1</v>
-      </c>
-      <c r="H17" s="0">
-        <v>0</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1471,27 +1455,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F18" s="1">
-        <v>30</v>
-      </c>
-      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="0">
         <v>2</v>
-      </c>
-      <c r="H18" s="0">
-        <v>0</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1502,27 +1484,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1">
-        <v>50</v>
-      </c>
-      <c r="G19" s="1">
-        <v>4</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G19" s="1"/>
       <c r="H19" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1533,21 +1513,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="0">
@@ -1555,7 +1535,7 @@
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -1564,21 +1544,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
         <v>35</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="1">
-        <v>75</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="0">
@@ -1586,7 +1566,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.05</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1595,21 +1575,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>125</v>
+        <v>45</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="0">
@@ -1617,7 +1597,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.14999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1629,166 +1609,8 @@
     <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="0">
-        <v>0</v>
-      </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="1">
-        <v>90008</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="1">
-        <v>90009</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="1">
-        <v>150</v>
-      </c>
-      <c r="G25" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="1">
-        <v>90009</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="1">
-        <v>200</v>
-      </c>
-      <c r="G26" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="1">
-        <v>90009</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="1">
-        <v>300</v>
-      </c>
-      <c r="G27" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0.0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,135 +15,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="43">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
   </si>
 </sst>
 </file>
@@ -658,16 +658,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
@@ -701,40 +701,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -742,13 +742,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
@@ -769,13 +769,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1">
         <v>10</v>
@@ -796,13 +796,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -823,13 +823,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -850,13 +850,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -928,46 +928,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -975,13 +975,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1">
         <v>4</v>
@@ -1006,13 +1006,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1">
         <v>6</v>
@@ -1037,13 +1037,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1097,13 +1097,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1126,13 +1126,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1155,13 +1155,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1186,16 +1186,16 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="0">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.23999999999999999</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1217,16 +1217,16 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="0">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1248,13 +1248,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1277,13 +1277,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1306,13 +1306,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1335,13 +1335,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1367,13 +1367,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1399,13 +1399,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1460,13 +1460,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1518,13 +1518,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1549,16 +1549,16 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="0">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.080000000000000004</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1580,13 +1580,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,132 +15,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="44">
   <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">저격 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">화염 포탑 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
     <t xml:space="preserve">냉기 포탑 강화</t>
   </si>
   <si>
     <t xml:space="preserve">미사일 포탑 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
+    <t xml:space="preserve">icon_id</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
@@ -658,16 +661,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
@@ -697,44 +700,45 @@
     <col min="6" max="6" width="15.640625" customWidth="1"/>
     <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
+    <col min="10" max="10" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -742,16 +746,16 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -769,20 +773,23 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>-0.20000000000000001</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -796,20 +803,23 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="J4" s="0">
+        <v>-0.29999999999999999</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -823,13 +833,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -850,13 +860,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -877,13 +887,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -928,46 +938,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="H1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -975,13 +985,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>4</v>
@@ -992,7 +1002,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1">
-        <v>0.014999999999999999</v>
+        <v>-0.014999999999999999</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1006,13 +1016,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1">
         <v>6</v>
@@ -1023,7 +1033,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="0">
-        <v>0.34999999999999998</v>
+        <v>-0.035000000000000003</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1037,13 +1047,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1054,7 +1064,7 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1">
-        <v>0.75</v>
+        <v>-0.075</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1068,13 +1078,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1097,13 +1107,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1126,13 +1136,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1155,13 +1165,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1172,7 +1182,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.10000000000000001</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1186,13 +1196,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1">
         <v>20</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.10000000000000001</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1217,13 +1227,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1">
         <v>24</v>
@@ -1234,7 +1244,7 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1">
-        <v>0.10000000000000001</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1248,13 +1258,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1277,13 +1287,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1306,13 +1316,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1335,13 +1345,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1367,13 +1377,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1399,13 +1409,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1431,13 +1441,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1460,13 +1470,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1489,13 +1499,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1518,13 +1528,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1549,13 +1559,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F21" s="1">
         <v>40</v>
@@ -1566,7 +1576,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.080000000000000004</v>
+        <v>-0.080000000000000004</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1580,13 +1590,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>
@@ -1597,7 +1607,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.12</v>
+        <v>-0.12</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -1,151 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId6"/>
+    <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격하는 적 수 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1} 감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 범위 &lt;color=#FF5851&gt;&lt;bounce&gt;{1} 증가&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;color=#FF5851&gt;&lt;bounce&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 &lt;bounce&gt;&lt;color=#FF5851&gt;{0} 증가&lt;/bounce&gt;&lt;/color&gt; 공격딜레이 &lt;color=#5196FF&gt;&lt;bounce&gt;{1}감소&lt;/bounce&gt;&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -190,7 +59,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -215,69 +84,11 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -362,6 +173,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -648,32 +527,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <v>upgrade_name</v>
+        <is>
+          <t xml:space="preserve">upgrade_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1">
         <v>80001</v>
       </c>
@@ -686,9 +583,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet2"/>
+  <sheetPr codeName="Sheet2">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="119.5703125" customWidth="1"/>
@@ -699,56 +599,101 @@
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <v>upgrade_name</v>
+        <is>
+          <t xml:space="preserve">upgrade_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <v>attack_damage</v>
+        <is>
+          <t xml:space="preserve">attack_damage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <v>attack_range</v>
+        <is>
+          <t xml:space="preserve">attack_range</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <v>attack_area</v>
+        <is>
+          <t xml:space="preserve">attack_area</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <v>attack_count</v>
+        <is>
+          <t xml:space="preserve">attack_count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <v>attack_interval</v>
+        <is>
+          <t xml:space="preserve">attack_interval</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <v>critical_chance</v>
+        <is>
+          <t xml:space="preserve">critical_chance</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <v>critical_damage</v>
+        <is>
+          <t xml:space="preserve">critical_damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+      <c r="B2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Name</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Desc</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+        </is>
       </c>
       <c r="F2" s="1">
         <v>10</v>
@@ -764,18 +709,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
+      <c r="B3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Name</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Desc</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+        </is>
       </c>
       <c r="F3" s="1">
         <v>10</v>
@@ -791,18 +745,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
+      <c r="B4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Name</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100001_Desc</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+        </is>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -818,18 +781,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
+      <c r="B5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Desc</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_288버켓</t>
+        </is>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -845,18 +817,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
+      <c r="B6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Name</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Desc</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_288버켓</t>
+        </is>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -872,18 +853,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
+      <c r="B7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">RUpgrade_100002_Desc</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">절대무적_요새_288버켓</t>
+        </is>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -899,7 +889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="6:7">
+    <row r="8">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
@@ -911,9 +901,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet3"/>
+  <sheetPr codeName="Sheet3">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="130.5703125" customWidth="1"/>
@@ -926,62 +919,113 @@
     <col min="10" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <v>upgrade_name</v>
+        <is>
+          <t xml:space="preserve">upgrade_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <v>max_hp</v>
+        <is>
+          <t xml:space="preserve">max_hp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <v>icon_id</v>
+        <is>
+          <t xml:space="preserve">icon_id</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <v>attack_damage</v>
+        <is>
+          <t xml:space="preserve">attack_damage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <v>attack_range</v>
+        <is>
+          <t xml:space="preserve">attack_range</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <v>attack_area</v>
+        <is>
+          <t xml:space="preserve">attack_area</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <v>attack_count</v>
+        <is>
+          <t xml:space="preserve">attack_count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <v>attack_interval</v>
+        <is>
+          <t xml:space="preserve">attack_interval</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <v>target_count</v>
+        <is>
+          <t xml:space="preserve">target_count</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <v>critical_chance</v>
+        <is>
+          <t xml:space="preserve">critical_chance</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <v>critical_damage</v>
+        <is>
+          <t xml:space="preserve">critical_damage</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <v>passive_skill_data_id</v>
+        <is>
+          <t xml:space="preserve">passive_skill_data_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
+      <c r="B2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Name</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Desc</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        </is>
       </c>
       <c r="F2" s="1">
         <v>4</v>
@@ -992,7 +1036,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1">
-        <v>0.014999999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1001,18 +1045,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>7</v>
+      <c r="B3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Name</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Desc</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        </is>
       </c>
       <c r="F3" s="1">
         <v>6</v>
@@ -1023,7 +1076,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="0">
-        <v>0.34999999999999998</v>
+        <v>0.35</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1032,18 +1085,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
+      <c r="B4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Name</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90001_Desc</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_08_UI</t>
+        </is>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1063,18 +1125,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
+      <c r="B5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Name</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Desc</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        </is>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1092,18 +1163,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
+      <c r="B6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Name</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Desc</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        </is>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1121,18 +1201,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>4</v>
+      <c r="B7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Name</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90002_Desc</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_05_UI</t>
+        </is>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1150,18 +1239,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>6</v>
+      <c r="B8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Name</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Desc</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        </is>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1172,7 +1270,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1181,18 +1279,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>6</v>
+      <c r="B9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Name</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Desc</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        </is>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1203,7 +1310,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.23999999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1212,18 +1319,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
+      <c r="B10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Name</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90003_Desc</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_10_UI</t>
+        </is>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1243,18 +1359,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11">
       <c r="A11" s="1">
         <v>90004</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
+      <c r="B11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Name</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Desc</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_288_19_UI</t>
+        </is>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1272,18 +1397,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
+      <c r="B12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Name</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Desc</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_288_19_UI</t>
+        </is>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1301,18 +1435,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
+      <c r="B13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Name</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90004_Desc</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_288_19_UI</t>
+        </is>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1330,18 +1473,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14">
       <c r="A14" s="1">
         <v>90005</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>5</v>
+      <c r="B14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Name</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Desc</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        </is>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1362,18 +1514,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>5</v>
+      <c r="B15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Name</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Desc</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        </is>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1394,18 +1555,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>5</v>
+      <c r="B16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Name</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90005_Desc</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_16_UI</t>
+        </is>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1426,18 +1596,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17">
       <c r="A17" s="1">
         <v>90006</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
+      <c r="B17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Name</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Desc</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        </is>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1455,18 +1634,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>10</v>
+      <c r="B18" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Name</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Desc</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        </is>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1484,18 +1672,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19">
       <c r="A19" s="1">
         <v>90006</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>10</v>
+      <c r="B19" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Name</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90006_Desc</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_MEL_14_UI</t>
+        </is>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1513,18 +1710,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20">
       <c r="A20" s="1">
         <v>90007</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>3</v>
+      <c r="B20" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Name</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Desc</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        </is>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1544,18 +1750,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21">
       <c r="A21" s="1">
         <v>90007</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>3</v>
+      <c r="B21" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Name</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Desc</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        </is>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1566,7 +1781,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1575,18 +1790,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22">
       <c r="A22" s="1">
         <v>90007</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>3</v>
+      <c r="B22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Name</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">TUpgrade_90007_Desc</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">Weapon_KMD_12_UI</t>
+        </is>
       </c>
       <c r="F22" s="1">
         <v>45</v>
@@ -1597,7 +1821,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1606,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="6:10">
+    <row r="23">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -1,20 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
+  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="600" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="2" r:id="rId5"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="3" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -59,7 +184,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -84,11 +209,69 @@
       </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+  <cellStyleXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -173,74 +356,6 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -527,50 +642,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet1">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="1" max="1" width="15.78515625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <v>upgrade_name</v>
-        <is>
-          <t xml:space="preserve">upgrade_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="1">
         <v>80001</v>
       </c>
@@ -583,12 +680,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet2">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="119.5703125" customWidth="1"/>
@@ -599,101 +693,56 @@
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <v>upgrade_name</v>
-        <is>
-          <t xml:space="preserve">upgrade_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <v>attack_area</v>
-        <is>
-          <t xml:space="preserve">attack_area</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Name</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Desc</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F2" s="1">
         <v>10</v>
@@ -709,27 +758,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Name</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Desc</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F3" s="1">
         <v>10</v>
@@ -745,27 +785,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Name</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100001_Desc</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -781,27 +812,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Name</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Desc</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_288버켓</t>
-        </is>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -817,27 +839,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Name</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Desc</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_288버켓</t>
-        </is>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -853,27 +866,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Name</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">RUpgrade_100002_Desc</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">절대무적_요새_288버켓</t>
-        </is>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -889,7 +893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="6:7">
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
@@ -901,12 +905,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet3">
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:O23"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="3" width="130.5703125" customWidth="1"/>
@@ -919,116 +920,65 @@
     <col min="10" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <v>upgrade_name</v>
-        <is>
-          <t xml:space="preserve">upgrade_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <v>max_hp</v>
-        <is>
-          <t xml:space="preserve">max_hp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <v>icon_id</v>
-        <is>
-          <t xml:space="preserve">icon_id</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <v>attack_damage</v>
-        <is>
-          <t xml:space="preserve">attack_damage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <v>attack_range</v>
-        <is>
-          <t xml:space="preserve">attack_range</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <v>attack_area</v>
-        <is>
-          <t xml:space="preserve">attack_area</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <v>attack_count</v>
-        <is>
-          <t xml:space="preserve">attack_count</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <v>attack_interval</v>
-        <is>
-          <t xml:space="preserve">attack_interval</t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <v>target_count</v>
-        <is>
-          <t xml:space="preserve">target_count</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <v>critical_chance</v>
-        <is>
-          <t xml:space="preserve">critical_chance</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <v>critical_damage</v>
-        <is>
-          <t xml:space="preserve">critical_damage</t>
-        </is>
-      </c>
-      <c r="N1" s="0" t="inlineStr">
-        <v>passive_skill_data_id</v>
-        <is>
-          <t xml:space="preserve">passive_skill_data_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Name</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Desc</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
-        </is>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -1036,7 +986,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1045,30 +995,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Name</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Desc</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F3" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
@@ -1076,7 +1017,7 @@
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="0">
-        <v>0.35</v>
+        <v>-0.020000000000000001</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1085,30 +1026,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Name</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90001_Desc</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_08_UI</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
@@ -1116,7 +1048,7 @@
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1">
-        <v>0.75</v>
+        <v>-0.029999999999999999</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1125,27 +1057,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>90002</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Name</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Desc</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
-        </is>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1163,27 +1086,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>90002</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Name</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Desc</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
-        </is>
+      <c r="B6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1201,27 +1115,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>90002</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Name</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90002_Desc</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_05_UI</t>
-        </is>
+      <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1239,27 +1144,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>90003</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Name</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Desc</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
-        </is>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1270,7 +1166,7 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1">
-        <v>0.1</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1279,27 +1175,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>90003</v>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Name</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Desc</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
-        </is>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1310,7 +1197,7 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1">
-        <v>0.24</v>
+        <v>-0.23999999999999999</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1319,27 +1206,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>90003</v>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Name</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90003_Desc</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_10_UI</t>
-        </is>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1359,27 +1237,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>90004</v>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Name</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Desc</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
-        </is>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1397,27 +1266,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>90004</v>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Name</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Desc</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
-        </is>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1435,27 +1295,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>90004</v>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Name</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90004_Desc</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_288_19_UI</t>
-        </is>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1473,27 +1324,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>90005</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Name</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Desc</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
-        </is>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1514,27 +1356,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>90005</v>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Name</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Desc</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
-        </is>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1555,27 +1388,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>90005</v>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Name</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90005_Desc</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_16_UI</t>
-        </is>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1596,27 +1420,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>90006</v>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Name</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Desc</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
-        </is>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1634,27 +1449,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:13">
       <c r="A18" s="1">
         <v>90006</v>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Name</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Desc</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
-        </is>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1672,27 +1478,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:13">
       <c r="A19" s="1">
         <v>90006</v>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Name</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90006_Desc</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_MEL_14_UI</t>
-        </is>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1710,27 +1507,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:13">
       <c r="A20" s="1">
         <v>90007</v>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Name</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Desc</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
-        </is>
+      <c r="B20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1750,27 +1538,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:13">
       <c r="A21" s="1">
         <v>90007</v>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Name</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Desc</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
-        </is>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1781,7 +1560,7 @@
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1">
-        <v>0.1</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -1790,27 +1569,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:13">
       <c r="A22" s="1">
         <v>90007</v>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Name</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">TUpgrade_90007_Desc</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Weapon_KMD_12_UI</t>
-        </is>
+      <c r="B22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>
@@ -1821,7 +1591,7 @@
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1">
-        <v>0.1</v>
+        <v>-0.10000000000000001</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -1830,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="6:10">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="41">
   <si>
     <t xml:space="preserve">RUpgrade_100001_Desc</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,129 +15,129 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
   <si>
     <t xml:space="preserve">RUpgrade_100001_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUpgrade_100002_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">RUpgrade_100002_Name</t>
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
   </si>
 </sst>
 </file>
@@ -652,19 +652,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -691,44 +691,45 @@
     <col min="6" max="6" width="15.640625" customWidth="1"/>
     <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
+    <col min="10" max="10" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>28</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -736,16 +737,16 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -763,20 +764,23 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>-0.20000000000000001</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -790,20 +794,23 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="J4" s="0">
+        <v>-0.29999999999999999</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -817,13 +824,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -844,20 +851,20 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
@@ -871,20 +878,20 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -922,46 +929,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="0" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -969,13 +976,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1000,13 +1007,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1031,13 +1038,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1062,13 +1069,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1091,13 +1098,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1120,13 +1127,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1149,13 +1156,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1180,13 +1187,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1211,13 +1218,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1242,13 +1249,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1271,13 +1278,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1300,13 +1307,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1329,13 +1336,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1361,13 +1368,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1393,13 +1400,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1425,13 +1432,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1454,13 +1461,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1483,13 +1490,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1512,13 +1519,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1543,13 +1550,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1574,13 +1581,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="41">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="41">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="41">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="41">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="41">
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,129 +15,129 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>
   <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
     <t xml:space="preserve">절대무적_요새_288버켓</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
     <t xml:space="preserve">upgrade_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">icon_id</t>
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
   </si>
 </sst>
 </file>
@@ -652,19 +652,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -696,40 +696,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -737,13 +737,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -764,13 +764,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -851,13 +851,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -878,13 +878,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -929,46 +929,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="0" t="s">
         <v>4</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -976,13 +976,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1007,13 +1007,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1038,13 +1038,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1069,16 +1069,16 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="0">
@@ -1098,16 +1098,16 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="0">
@@ -1127,16 +1127,16 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F7" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
@@ -1156,13 +1156,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1187,13 +1187,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1218,13 +1218,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1249,13 +1249,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1278,13 +1278,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1307,13 +1307,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1336,13 +1336,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
@@ -1368,13 +1368,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1">
         <v>4</v>
@@ -1400,13 +1400,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1461,13 +1461,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1490,13 +1490,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1519,13 +1519,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1550,13 +1550,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1581,13 +1581,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,7 +15,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="41">
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
   <si>
     <t xml:space="preserve">attack_count</t>
   </si>
@@ -38,106 +128,16 @@
     <t xml:space="preserve">attack_range</t>
   </si>
   <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
     <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
   </si>
 </sst>
 </file>
@@ -652,19 +652,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -696,40 +696,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -737,10 +737,10 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>10</v>
@@ -764,10 +764,10 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>10</v>
@@ -794,10 +794,10 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>10</v>
@@ -824,13 +824,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -851,13 +851,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -878,13 +878,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -929,46 +929,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -979,10 +979,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1010,10 +1010,10 @@
         <v>23</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1041,10 +1041,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1069,13 +1069,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1098,13 +1098,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1127,13 +1127,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1159,7 +1159,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>9</v>
@@ -1190,7 +1190,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>9</v>
@@ -1221,7 +1221,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
@@ -1249,13 +1249,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1278,13 +1278,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1307,13 +1307,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1336,16 +1336,16 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="0">
@@ -1368,16 +1368,16 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F15" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="0">
@@ -1400,16 +1400,16 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="0">
@@ -1418,7 +1418,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -1432,13 +1432,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1461,13 +1461,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1490,13 +1490,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1519,13 +1519,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1550,13 +1550,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1581,13 +1581,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,7 +15,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
   </si>
@@ -23,121 +140,7 @@
     <t xml:space="preserve">RUpgrade_100002_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
     <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
   </si>
 </sst>
 </file>
@@ -652,19 +655,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -681,7 +684,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
@@ -691,56 +694,59 @@
     <col min="6" max="6" width="15.640625" customWidth="1"/>
     <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
-    <col min="10" max="10" width="9.00390625" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>10</v>
@@ -758,16 +764,19 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>10</v>
@@ -788,16 +797,19 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>10</v>
@@ -818,46 +830,46 @@
       <c r="L4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1">
         <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="0">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -866,38 +878,32 @@
       <c r="H6" s="0">
         <v>1</v>
       </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="M7" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="6:7">
@@ -929,46 +935,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="N1" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -976,13 +982,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1007,13 +1013,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1038,13 +1044,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1069,13 +1075,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -1098,13 +1104,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1">
         <v>2</v>
@@ -1127,13 +1133,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
@@ -1156,13 +1162,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1187,13 +1193,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1218,13 +1224,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1249,13 +1255,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1278,13 +1284,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1307,13 +1313,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1336,13 +1342,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1368,13 +1374,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -1400,13 +1406,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1432,13 +1438,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1461,13 +1467,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1490,13 +1496,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1519,13 +1525,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1550,13 +1556,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1581,13 +1587,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="42">
   <si>
     <t xml:space="preserve">id</t>
   </si>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,104 +15,119 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUpgrade_90006_Name</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_KMD_08_UI</t>
   </si>
   <si>
     <t xml:space="preserve">TUpgrade_90005_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUpgrade_90004_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
@@ -126,21 +141,6 @@
   </si>
   <si>
     <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
   </si>
 </sst>
 </file>
@@ -655,19 +655,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -694,48 +694,48 @@
     <col min="6" max="6" width="15.640625" customWidth="1"/>
     <col min="7" max="8" width="9.00390625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
-    <col min="10" max="12" width="9.00390625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -743,13 +743,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -773,13 +773,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -839,13 +839,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -863,20 +863,20 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="0">
         <v>10</v>
@@ -887,23 +887,23 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="0">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="6:7">
@@ -935,46 +935,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -982,13 +982,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1013,13 +1013,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1044,13 +1044,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1075,13 +1075,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1104,13 +1104,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -1133,13 +1133,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -1162,13 +1162,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1193,13 +1193,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1224,13 +1224,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1255,13 +1255,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1284,13 +1284,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1313,13 +1313,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1342,13 +1342,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -1406,13 +1406,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1438,13 +1438,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1467,13 +1467,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1496,13 +1496,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F19" s="1">
         <v>20</v>
@@ -1525,13 +1525,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1556,13 +1556,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1587,13 +1587,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="28545" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Train_Upgrade_Data" sheetId="1" r:id="rId4"/>
@@ -15,7 +15,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
   <si>
     <t xml:space="preserve">절대무적_요새_288버켓</t>
   </si>
@@ -23,124 +104,43 @@
     <t xml:space="preserve">attack_count</t>
   </si>
   <si>
-    <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
+    <t xml:space="preserve">attack_range</t>
   </si>
   <si>
     <t xml:space="preserve">attack_interval</t>
   </si>
   <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
     <t xml:space="preserve">critical_chance</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
   </si>
 </sst>
 </file>
@@ -655,19 +655,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -699,43 +699,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -743,13 +743,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -773,13 +773,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -806,13 +806,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -839,13 +839,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -863,13 +863,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -887,13 +887,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -935,46 +935,46 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N1" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -982,13 +982,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1013,13 +1013,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1044,13 +1044,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1075,13 +1075,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1104,13 +1104,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -1133,13 +1133,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -1162,13 +1162,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1">
         <v>10</v>
@@ -1193,13 +1193,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1">
         <v>10</v>
@@ -1224,13 +1224,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
         <v>20</v>
@@ -1255,13 +1255,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1284,13 +1284,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1313,13 +1313,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1342,13 +1342,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -1406,13 +1406,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1438,16 +1438,16 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="0">
@@ -1467,20 +1467,20 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1">
         <v>30</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1496,20 +1496,20 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1525,13 +1525,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1556,13 +1556,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1587,13 +1587,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,132 +15,132 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
   <si>
     <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapon_KMD_12_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUpgrade_90001_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_10_UI</t>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">TUpgrade_90007_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUpgrade_90005_Desc</t>
   </si>
   <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_288_19_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">TUpgrade_90006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weapon_KMD_08_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_12_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">slow_rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">critical_damage</t>
   </si>
   <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
     <t xml:space="preserve">attack_damage</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
     <t xml:space="preserve">upgrade_name</t>
   </si>
   <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
     <t xml:space="preserve">target_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slow_rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_skill_data_id</t>
   </si>
 </sst>
 </file>
@@ -658,16 +658,16 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -702,40 +702,40 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>23</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -743,16 +743,16 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -773,24 +773,21 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
         <v>1</v>
       </c>
-      <c r="J3" s="0">
-        <v>-0.20000000000000001</v>
-      </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
@@ -806,23 +803,20 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
-        <v>2</v>
-      </c>
-      <c r="J4" s="0">
-        <v>-0.29999999999999999</v>
+        <v>1</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -839,13 +833,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -863,13 +857,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -887,13 +881,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -938,43 +932,43 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -982,13 +976,13 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1">
         <v>5</v>
@@ -1013,13 +1007,13 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F3" s="1">
         <v>8</v>
@@ -1044,13 +1038,13 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1">
         <v>9</v>
@@ -1075,13 +1069,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1104,13 +1098,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -1133,13 +1127,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -1162,25 +1156,23 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="0">
         <v>0</v>
       </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="1">
-        <v>-0.10000000000000001</v>
-      </c>
+      <c r="J8" s="1"/>
       <c r="L8" s="1">
         <v>0</v>
       </c>
@@ -1193,25 +1185,23 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="0">
         <v>0</v>
       </c>
       <c r="I9" s="1"/>
-      <c r="J9" s="1">
-        <v>-0.23999999999999999</v>
-      </c>
+      <c r="J9" s="1"/>
       <c r="L9" s="1">
         <v>0</v>
       </c>
@@ -1224,25 +1214,23 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="0">
         <v>0</v>
       </c>
       <c r="I10" s="1"/>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
+      <c r="J10" s="1"/>
       <c r="L10" s="1">
         <v>0</v>
       </c>
@@ -1255,13 +1243,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1284,13 +1272,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1313,13 +1301,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1342,13 +1330,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1374,13 +1362,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -1406,13 +1394,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1438,13 +1426,13 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
         <v>15</v>
@@ -1467,13 +1455,13 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>30</v>
@@ -1496,13 +1484,13 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F19" s="1">
         <v>55</v>
@@ -1525,13 +1513,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1556,13 +1544,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1587,13 +1575,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,77 +15,104 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_14_UI</t>
+  </si>
   <si>
     <t xml:space="preserve">Weapon_KMD_10_UI</t>
   </si>
   <si>
-    <t xml:space="preserve">Weapon_MEL_14_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
+    <t xml:space="preserve">TUpgrade_90007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_288_19_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_05_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90005_Desc</t>
   </si>
   <si>
     <t xml:space="preserve">Weapon_KMD_12_UI</t>
   </si>
   <si>
+    <t xml:space="preserve">Weapon_KMD_08_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon_MEL_16_UI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUpgrade_90007_Name</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUpgrade_90006_Desc</t>
   </si>
   <si>
-    <t xml:space="preserve">TUpgrade_90002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_05_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_288_19_UI</t>
-  </si>
-  <si>
     <t xml:space="preserve">TUpgrade_90006_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">TUpgrade_90004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUpgrade_90002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_MEL_16_UI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon_KMD_08_UI</t>
-  </si>
-  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">절대무적_요새_288버켓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critical_chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+  </si>
+  <si>
     <t xml:space="preserve">slow_rate</t>
   </si>
   <si>
@@ -95,52 +122,25 @@
     <t xml:space="preserve">attack_area</t>
   </si>
   <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">max_hp</t>
   </si>
   <si>
-    <t xml:space="preserve">icon_id</t>
+    <t xml:space="preserve">RUpgrade_100001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUpgrade_100001_Name</t>
   </si>
   <si>
     <t xml:space="preserve">RUpgrade_100002_Name</t>
   </si>
   <si>
+    <t xml:space="preserve">RUpgrade_100002_Desc</t>
+  </si>
+  <si>
     <t xml:space="preserve">passive_skill_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUpgrade_100001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">critical_chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">절대무적_요새_288버켓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
   </si>
 </sst>
 </file>
@@ -658,16 +658,16 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -702,40 +702,40 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="0" t="s">
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="M1" s="0" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -743,13 +743,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>20</v>
@@ -773,13 +773,13 @@
         <v>100001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1">
         <v>30</v>
@@ -803,13 +803,13 @@
         <v>100001</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>50</v>
@@ -833,13 +833,13 @@
         <v>100002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -857,13 +857,13 @@
         <v>100002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -881,13 +881,13 @@
         <v>100002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -932,43 +932,43 @@
         <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1" s="0" t="s">
+      <c r="K1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="0" t="s">
+      <c r="N1" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="0" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -976,16 +976,16 @@
         <v>90001</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="0">
@@ -1007,16 +1007,16 @@
         <v>90001</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
         <v>6</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="1">
-        <v>8</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="0">
@@ -1038,16 +1038,16 @@
         <v>90001</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="0">
@@ -1069,13 +1069,13 @@
         <v>90002</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1098,13 +1098,13 @@
         <v>90002</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -1127,13 +1127,13 @@
         <v>90002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1">
         <v>6</v>
@@ -1156,13 +1156,13 @@
         <v>90003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1">
         <v>15</v>
@@ -1185,13 +1185,13 @@
         <v>90003</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1">
         <v>30</v>
@@ -1214,13 +1214,13 @@
         <v>90003</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1">
         <v>55</v>
@@ -1243,13 +1243,13 @@
         <v>90004</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1">
         <v>25</v>
@@ -1272,13 +1272,13 @@
         <v>90004</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1">
         <v>50</v>
@@ -1301,13 +1301,13 @@
         <v>90004</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1">
         <v>75</v>
@@ -1330,13 +1330,13 @@
         <v>90005</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1362,13 +1362,13 @@
         <v>90005</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F15" s="1">
         <v>2</v>
@@ -1394,13 +1394,13 @@
         <v>90005</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F16" s="1">
         <v>4</v>
@@ -1426,10 +1426,10 @@
         <v>90006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>1</v>
@@ -1455,10 +1455,10 @@
         <v>90006</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>1</v>
@@ -1484,10 +1484,10 @@
         <v>90006</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>1</v>
@@ -1513,13 +1513,13 @@
         <v>90007</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F20" s="1">
         <v>25</v>
@@ -1544,13 +1544,13 @@
         <v>90007</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1">
         <v>35</v>
@@ -1575,13 +1575,13 @@
         <v>90007</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1">
         <v>45</v>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="44">
   <si>
     <t xml:space="preserve">절대무적_요새_멜리에스클래식_몸통뉴</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t xml:space="preserve">passive_skill_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">burst_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level</t>
   </si>
 </sst>
 </file>
@@ -684,7 +690,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
@@ -697,7 +703,7 @@
     <col min="10" max="13" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -737,8 +743,14 @@
       <c r="M1" s="0" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -748,27 +760,44 @@
       <c r="C2" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="1">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="0">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>100001</v>
       </c>
@@ -778,15 +807,26 @@
       <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="1">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="0">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
       <c r="K3" s="1">
         <v>0</v>
@@ -794,11 +834,17 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>100001</v>
       </c>
@@ -808,101 +854,559 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="0">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>1</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1">
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="1">
         <v>100002</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="0">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0">
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>10</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1">
+    <row r="14" spans="1:15">
+      <c r="A14" s="1">
         <v>100002</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="M6" s="0">
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1">
-        <v>100002</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="0">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="6:7">
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -913,7 +1417,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
@@ -927,7 +1431,7 @@
     <col min="10" max="11" width="9.00390625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -970,8 +1474,14 @@
       <c r="N1" s="0" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="O1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
@@ -981,28 +1491,44 @@
       <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="0">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
       <c r="L2" s="1">
         <v>0</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>90001</v>
       </c>
@@ -1012,19 +1538,29 @@
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="1">
-        <v>6</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="0">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="0">
-        <v>-0.020000000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1032,8 +1568,14 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>90001</v>
       </c>
@@ -1043,19 +1585,29 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="0">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
       <c r="J4" s="1">
-        <v>-0.029999999999999999</v>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <v>0</v>
       </c>
       <c r="L4" s="1">
         <v>0</v>
@@ -1063,549 +1615,2174 @@
       <c r="M4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="0">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
       <c r="L5" s="1">
         <v>0</v>
       </c>
       <c r="M5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
-        <v>90002</v>
+        <v>90001</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="0">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
+        <v>90001</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1">
+        <v>90001</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>-0.0519</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1">
         <v>90002</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="0">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="1">
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+      <c r="P10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-0.5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1">
         <v>90003</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.1304</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-0.2007</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.484</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="1">
         <v>15</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="0">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="1">
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="1">
         <v>90003</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="D22" s="1">
+        <v>0</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="1">
-        <v>30</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="H9" s="0">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="1">
-        <v>90003</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1.162</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1">
+        <v>25</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>-0.4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>0</v>
+      </c>
+      <c r="P26" s="1">
         <v>4</v>
       </c>
-      <c r="E10" s="1" t="s">
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
+        <v>2.047</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
+        <v>0</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1">
+        <v>-0.1273</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="0">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="1">
-        <v>90004</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="1" t="s">
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1">
+        <v>0</v>
+      </c>
+      <c r="O32" s="1">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1">
+        <v>-0.2121</v>
+      </c>
+      <c r="K33" s="1">
+        <v>0</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
+        <v>0</v>
+      </c>
+      <c r="P33" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
+      </c>
+      <c r="M35" s="1">
+        <v>0</v>
+      </c>
+      <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="I36" s="1">
+        <v>2</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
+      </c>
+      <c r="M36" s="1">
+        <v>0</v>
+      </c>
+      <c r="O36" s="1">
+        <v>0</v>
+      </c>
+      <c r="P36" s="1">
         <v>7</v>
       </c>
-      <c r="F11" s="1">
-        <v>25</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="0">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="1">
-        <v>90004</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>-0.2273</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>0</v>
+      </c>
+      <c r="P40" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>-0.2964</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1.404</v>
+      </c>
+      <c r="I43" s="1">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
         <v>7</v>
       </c>
-      <c r="F12" s="1">
-        <v>50</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="0">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="1">
-        <v>90004</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1" t="s">
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="1">
+        <v>6</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>-0.1091</v>
+      </c>
+      <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="1">
+        <v>12</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>-0.1818</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="1">
+        <v>22</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>-0.1818</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" s="1">
+        <v>90007</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>-0.2257</v>
+      </c>
+      <c r="K50" s="1">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
         <v>7</v>
       </c>
-      <c r="F13" s="1">
-        <v>75</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="0">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="1">
-        <v>90005</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="0">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="0">
-        <v>1</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="1">
-        <v>90005</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="0">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="0">
-        <v>1</v>
-      </c>
-      <c r="L15" s="1">
-        <v>0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="1">
-        <v>90005</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4</v>
-      </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="0">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="0">
-        <v>1</v>
-      </c>
-      <c r="L16" s="1">
-        <v>0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="1">
-        <v>90006</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>15</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="0">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="1">
-        <v>90006</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>30</v>
-      </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="0">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="L18" s="1">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="1">
-        <v>90006</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>55</v>
-      </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="0">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="L19" s="1">
-        <v>0</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="1">
-        <v>90007</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="1">
-        <v>25</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="0">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="1">
-        <v>90007</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="1">
-        <v>35</v>
-      </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="0">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="1">
-        <v>90007</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1">
-        <v>45</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="0">
-        <v>0</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1">
-        <v>-0.10000000000000001</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="6:10">
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Assets/02_Resources/Data/TrainUpgradeData.xlsx
+++ b/Assets/02_Resources/Data/TrainUpgradeData.xlsx
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="1">
         <v>0</v>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="1">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
